--- a/data/SupplementalTables/STable16.TurboID-explant-functions.xlsx
+++ b/data/SupplementalTables/STable16.TurboID-explant-functions.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allim\Desktop\TurboID\SupplementalTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\allim\Desktop\TurboID\SupplementalTables_v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9633C8C7-93ED-4051-86A7-0DD10191BDA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3ABC95-E782-4532-8828-AD4ADFD225C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="2745" windowWidth="14460" windowHeight="11295" xr2:uid="{A83E73FD-9155-4B49-9FCA-067D5B3B0765}"/>
+    <workbookView xWindow="-26325" yWindow="480" windowWidth="22755" windowHeight="13530" activeTab="4" xr2:uid="{A83E73FD-9155-4B49-9FCA-067D5B3B0765}"/>
   </bookViews>
   <sheets>
     <sheet name=" MF_DOWN" sheetId="3" r:id="rId1"/>
     <sheet name=" MF_UP" sheetId="4" r:id="rId2"/>
     <sheet name=" BP_DOWN" sheetId="1" r:id="rId3"/>
     <sheet name=" BP_UP" sheetId="2" r:id="rId4"/>
+    <sheet name="README" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="58">
   <si>
     <t>ID</t>
   </si>
@@ -192,6 +193,27 @@
   </si>
   <si>
     <t>GO:0015171</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>MF</t>
+  </si>
+  <si>
+    <t>BP</t>
+  </si>
+  <si>
+    <t>GO molecular function enrichments</t>
+  </si>
+  <si>
+    <t>GO biological pathway enrichments</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Empty sheet = no significant pathways</t>
   </si>
 </sst>
 </file>
@@ -1037,4 +1059,50 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F611204A-732A-49F9-A59F-0D84A6B38277}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>